--- a/events/LaSeu_2018_WC/LaSeu_2018_WC_start.xlsx
+++ b/events/LaSeu_2018_WC/LaSeu_2018_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W624"/>
+  <dimension ref="A1:AC616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1148,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -1176,7 +1206,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -1234,7 +1264,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -1292,7 +1322,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -1350,7 +1380,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -1408,7 +1438,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -1466,7 +1496,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -1524,7 +1554,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -1582,7 +1612,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -1640,7 +1670,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -1698,7 +1728,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -1756,7 +1786,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -1814,7 +1844,7 @@
           <t>NOWAK Przemyslaw</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>43974</t>
         </is>
@@ -1872,7 +1902,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -1930,7 +1960,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -1988,7 +2018,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -2046,7 +2076,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -2104,7 +2134,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -2162,7 +2192,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -2220,7 +2250,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -2278,7 +2308,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -2336,7 +2366,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -2394,7 +2424,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -2452,7 +2482,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -2510,7 +2540,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -2568,7 +2598,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -2626,7 +2656,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -2684,7 +2714,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -2742,7 +2772,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -2800,7 +2830,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -2858,7 +2888,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -2916,7 +2946,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -2974,7 +3004,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -3032,7 +3062,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -3090,7 +3120,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -3148,7 +3178,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -3206,7 +3236,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -3264,7 +3294,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -3322,7 +3352,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -3380,7 +3410,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -3438,7 +3468,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -3496,7 +3526,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -3554,7 +3584,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -3612,7 +3642,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -3670,7 +3700,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -3728,7 +3758,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -3786,7 +3816,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3844,7 +3874,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -3902,7 +3932,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -3960,7 +3990,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -4018,7 +4048,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -4076,7 +4106,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -4134,7 +4164,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -4192,7 +4222,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -4250,7 +4280,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4308,7 +4338,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4366,7 +4396,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -4424,7 +4454,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -4482,7 +4512,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -4540,7 +4570,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -4598,7 +4628,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -4656,7 +4686,7 @@
           <t>MALAGUTI Francesca</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>77362</t>
         </is>
@@ -4714,7 +4744,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -4772,7 +4802,7 @@
           <t>PATERSON Claudia</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>59997</t>
         </is>
@@ -4830,7 +4860,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -4888,7 +4918,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -4946,7 +4976,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -5004,7 +5034,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -5062,7 +5092,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -5120,7 +5150,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -5178,7 +5208,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -5236,7 +5266,7 @@
           <t>MURZOVA Lucia</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>60316</t>
         </is>
@@ -5294,7 +5324,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -5352,7 +5382,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -5410,7 +5440,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -5468,7 +5498,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -5526,7 +5556,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -5584,7 +5614,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -5642,7 +5672,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -5700,7 +5730,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -5758,7 +5788,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -5816,7 +5846,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -5874,7 +5904,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -5932,7 +5962,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -5990,7 +6020,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -6048,7 +6078,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -6106,7 +6136,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -6164,7 +6194,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -6222,7 +6252,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -6280,7 +6310,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -6338,7 +6368,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -6396,7 +6426,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -6454,7 +6484,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -6512,7 +6542,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -6570,7 +6600,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -6628,7 +6658,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -6686,7 +6716,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -6744,7 +6774,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -6802,7 +6832,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -6860,7 +6890,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -6918,7 +6948,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6976,7 +7006,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -7034,7 +7064,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -7092,7 +7122,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -7150,7 +7180,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -7208,7 +7238,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -7266,7 +7296,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -7324,7 +7354,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -7382,7 +7412,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -7440,7 +7470,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -7498,7 +7528,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -7556,7 +7586,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -7614,7 +7644,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -7672,7 +7702,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -7730,7 +7760,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -7788,7 +7818,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -7846,7 +7876,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -7904,7 +7934,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -7962,7 +7992,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -8020,7 +8050,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -8078,7 +8108,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -8136,7 +8166,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -8194,7 +8224,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -8252,7 +8282,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -8310,7 +8340,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -8368,7 +8398,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -8426,7 +8456,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -8484,7 +8514,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -8542,7 +8572,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -8600,7 +8630,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -8658,7 +8688,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -8716,7 +8746,7 @@
           <t>NOWAK Przemyslaw</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>43974</t>
         </is>
@@ -8774,7 +8804,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -8832,7 +8862,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -8890,7 +8920,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -8948,7 +8978,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -9006,7 +9036,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -9064,7 +9094,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -9122,7 +9152,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -9180,7 +9210,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -9238,7 +9268,7 @@
           <t>CRAWFORD Brodie</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
@@ -9296,7 +9326,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -9354,7 +9384,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -9412,7 +9442,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -9470,7 +9500,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -9528,7 +9558,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -9586,7 +9616,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -9644,7 +9674,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -9702,7 +9732,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -9760,7 +9790,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -9818,7 +9848,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -9876,7 +9906,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -9934,7 +9964,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -9992,7 +10022,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -10050,7 +10080,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -10108,7 +10138,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -10166,7 +10196,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -10224,7 +10254,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -10282,7 +10312,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -10340,7 +10370,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -10398,7 +10428,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -10456,7 +10486,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -10514,7 +10544,7 @@
           <t>MALAGUTI Francesca</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>77362</t>
         </is>
@@ -10572,7 +10602,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -10630,7 +10660,7 @@
           <t>PATERSON Claudia</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>59997</t>
         </is>
@@ -10688,7 +10718,7 @@
           <t>FLEPP Milena</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>73274</t>
         </is>
@@ -10746,7 +10776,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -10804,7 +10834,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -10862,7 +10892,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -10920,7 +10950,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -10978,7 +11008,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -11036,7 +11066,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -11094,7 +11124,7 @@
           <t>MURZOVA Lucia</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>60316</t>
         </is>
@@ -11152,7 +11182,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -11210,7 +11240,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -11268,7 +11298,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -11326,7 +11356,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -11384,7 +11414,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -11442,7 +11472,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -11500,7 +11530,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -11558,7 +11588,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -11616,7 +11646,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -11674,7 +11704,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -11732,7 +11762,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -11790,7 +11820,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -11848,7 +11878,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -11906,7 +11936,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -11964,7 +11994,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -12022,7 +12052,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -12080,7 +12110,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -12138,7 +12168,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -12196,7 +12226,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -12254,7 +12284,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -12312,7 +12342,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -12370,7 +12400,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -12428,7 +12458,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -12486,7 +12516,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -12544,7 +12574,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -12602,7 +12632,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -12660,7 +12690,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -12930,7 +12960,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -12988,7 +13018,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -13046,7 +13076,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -13104,7 +13134,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -13162,7 +13192,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -13220,7 +13250,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -13278,7 +13308,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -13336,7 +13366,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -13394,7 +13424,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -13452,7 +13482,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -13510,7 +13540,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -13568,7 +13598,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -13626,7 +13656,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -13684,7 +13714,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13742,7 +13772,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -13800,7 +13830,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -13858,7 +13888,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -13916,7 +13946,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -13974,7 +14004,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -14032,7 +14062,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -14090,7 +14120,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -14148,7 +14178,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -14206,7 +14236,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -14264,7 +14294,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -14322,7 +14352,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -14380,7 +14410,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -14438,7 +14468,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -14496,7 +14526,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -14554,7 +14584,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -14612,7 +14642,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -14670,7 +14700,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -14728,7 +14758,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -14786,7 +14816,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -14844,7 +14874,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -14902,7 +14932,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -14960,7 +14990,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -15018,7 +15048,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -15076,7 +15106,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -15134,7 +15164,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -15192,7 +15222,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -15250,7 +15280,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -15308,7 +15338,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -15366,7 +15396,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -15424,7 +15454,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -15482,7 +15512,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -15540,7 +15570,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -15598,7 +15628,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -15656,7 +15686,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -15714,7 +15744,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -15772,7 +15802,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -15830,7 +15860,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -15888,7 +15918,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -15946,7 +15976,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -16004,7 +16034,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -16062,7 +16092,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -16120,7 +16150,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -16178,7 +16208,7 @@
           <t>MAGALHAE Alexandre</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>69116</t>
         </is>
@@ -16236,7 +16266,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -16294,7 +16324,7 @@
           <t>POLACZYK Rafal</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35083</t>
         </is>
@@ -16352,7 +16382,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -16410,7 +16440,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -16468,7 +16498,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -16526,7 +16556,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -16584,7 +16614,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -16642,7 +16672,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -16700,7 +16730,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -16758,7 +16788,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -16816,7 +16846,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -16874,7 +16904,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -16932,7 +16962,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -16990,7 +17020,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -17048,7 +17078,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -17106,7 +17136,7 @@
           <t>STRAUSS Thomas</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>55113</t>
         </is>
@@ -17164,7 +17194,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -17222,7 +17252,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -17280,7 +17310,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -17338,7 +17368,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -17396,7 +17426,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -17454,7 +17484,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -17512,7 +17542,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -17570,7 +17600,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -17628,7 +17658,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -17686,7 +17716,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -17744,7 +17774,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17802,7 +17832,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -17860,7 +17890,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -17918,7 +17948,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -17976,7 +18006,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -18034,7 +18064,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -18092,7 +18122,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -18150,7 +18180,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -18208,7 +18238,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -18266,7 +18296,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -18324,7 +18354,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -18382,7 +18412,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -18440,7 +18470,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -18498,7 +18528,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -18556,7 +18586,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -18614,7 +18644,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -18672,7 +18702,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -18730,7 +18760,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -18788,7 +18818,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -18846,7 +18876,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -18904,7 +18934,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -18962,7 +18992,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -19020,7 +19050,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -19078,7 +19108,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -19136,7 +19166,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -19194,7 +19224,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -19252,7 +19282,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -19310,7 +19340,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -19368,7 +19398,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -19426,7 +19456,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -19484,7 +19514,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -19542,7 +19572,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -19600,7 +19630,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -19658,7 +19688,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -19716,7 +19746,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -19774,7 +19804,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -19832,7 +19862,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -19890,7 +19920,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -19948,7 +19978,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -20006,7 +20036,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -20064,7 +20094,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -20122,7 +20152,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -20180,7 +20210,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -20238,7 +20268,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -20296,7 +20326,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -20354,7 +20384,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -20412,7 +20442,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -20470,7 +20500,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -20528,7 +20558,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -20586,7 +20616,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -20644,7 +20674,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -20702,7 +20732,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -20760,7 +20790,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -20818,7 +20848,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -20876,7 +20906,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -20934,7 +20964,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -20992,7 +21022,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -21050,7 +21080,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -21108,7 +21138,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -21166,7 +21196,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -21224,7 +21254,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -21282,7 +21312,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -21340,7 +21370,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -21398,7 +21428,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -21456,7 +21486,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -21514,7 +21544,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -21572,7 +21602,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -21630,7 +21660,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -21688,7 +21718,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -21746,7 +21776,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -21804,7 +21834,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -21862,7 +21892,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -21920,7 +21950,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -21978,7 +22008,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -22036,7 +22066,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -22094,7 +22124,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -22152,7 +22182,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -22210,7 +22240,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -22268,7 +22298,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -22326,7 +22356,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -22384,7 +22414,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -22442,7 +22472,7 @@
           <t>MAGALHAE Alexandre</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>69116</t>
         </is>
@@ -22500,7 +22530,7 @@
           <t>POLACZYK Rafal</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35083</t>
         </is>
@@ -22558,7 +22588,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -22616,7 +22646,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -22674,7 +22704,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -22732,7 +22762,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -22790,7 +22820,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -22848,7 +22878,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -22906,7 +22936,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -22964,7 +22994,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -23022,7 +23052,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -23080,7 +23110,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -23138,7 +23168,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -23196,7 +23226,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -23254,7 +23284,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -23312,7 +23342,7 @@
           <t>STRAUSS Thomas</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>55113</t>
         </is>
@@ -23370,7 +23400,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -23428,7 +23458,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -23486,7 +23516,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -23544,7 +23574,7 @@
           <t>PESTOV Ruslan</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>36138</t>
         </is>
@@ -23602,7 +23632,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -23660,7 +23690,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -23718,7 +23748,7 @@
           <t>DE DIONIGI Christian</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>43188</t>
         </is>
@@ -23776,7 +23806,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -23834,7 +23864,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -23892,7 +23922,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -23950,7 +23980,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -24008,7 +24038,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -24066,7 +24096,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -24124,7 +24154,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -24182,7 +24212,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -24240,7 +24270,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -24298,7 +24328,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -24356,7 +24386,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -24414,7 +24444,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -24472,7 +24502,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -24530,7 +24560,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -24588,7 +24618,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -24646,7 +24676,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -24704,7 +24734,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -24762,7 +24792,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -24820,7 +24850,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -24878,7 +24908,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -25143,7 +25173,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -25201,7 +25231,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -25259,7 +25289,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -25317,7 +25347,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -25375,7 +25405,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -25433,7 +25463,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -25491,7 +25521,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -25549,7 +25579,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -25607,7 +25637,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -25665,7 +25695,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -25723,7 +25753,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -25781,7 +25811,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -25839,7 +25869,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -25897,7 +25927,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -25955,7 +25985,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -26013,7 +26043,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -26071,7 +26101,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -26129,7 +26159,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -26187,7 +26217,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -26245,7 +26275,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -26303,7 +26333,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -26361,7 +26391,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -26419,7 +26449,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -26477,7 +26507,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -26535,7 +26565,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -26593,7 +26623,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -26651,7 +26681,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -26709,7 +26739,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -26767,7 +26797,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -26825,7 +26855,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -26883,7 +26913,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -26941,7 +26971,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -26999,7 +27029,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -27057,7 +27087,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -27115,7 +27145,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -27173,7 +27203,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -27231,7 +27261,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -27289,7 +27319,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -27347,7 +27377,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -27405,7 +27435,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -27463,7 +27493,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -27521,7 +27551,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -27579,7 +27609,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -27637,7 +27667,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -27695,7 +27725,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -27753,7 +27783,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -27811,7 +27841,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -27869,7 +27899,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -27927,7 +27957,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -27985,7 +28015,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -28043,7 +28073,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -28101,7 +28131,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -28159,7 +28189,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -28217,7 +28247,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -28275,7 +28305,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -28333,7 +28363,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -28391,7 +28421,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -28449,7 +28479,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -28507,7 +28537,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -28565,7 +28595,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -28633,7 +28663,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -28701,7 +28731,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -28769,7 +28799,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -28837,7 +28867,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -28905,7 +28935,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -28973,7 +29003,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -29041,7 +29071,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -29109,7 +29139,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -29177,7 +29207,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -29245,7 +29275,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -29313,7 +29343,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -29381,7 +29411,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -29449,7 +29479,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -29517,7 +29547,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -29585,7 +29615,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -29653,7 +29683,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -29721,7 +29751,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -29789,7 +29819,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -29857,7 +29887,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -29925,7 +29955,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -29988,12 +30018,12 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
       </c>
-      <c r="V508" t="inlineStr">
+      <c r="Y508" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -30056,12 +30086,12 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V509" t="inlineStr">
+      <c r="Y509" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -30124,12 +30154,12 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
       </c>
-      <c r="V510" t="inlineStr">
+      <c r="Y510" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -30192,7 +30222,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -30255,12 +30285,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V512" t="inlineStr">
+      <c r="Y512" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -30323,7 +30353,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V513" t="inlineStr">
+      <c r="Y513" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -30396,12 +30426,12 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
       </c>
-      <c r="V514" t="inlineStr">
+      <c r="Y514" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -30474,12 +30504,12 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
       </c>
-      <c r="V515" t="inlineStr">
+      <c r="Y515" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -30552,7 +30582,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V516" t="inlineStr">
+      <c r="Y516" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -30625,12 +30655,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V517" t="inlineStr">
+      <c r="Y517" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -30703,12 +30733,12 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V518" t="inlineStr">
+      <c r="Y518" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -30781,7 +30811,7 @@
           <t>STACH Aleksandra</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -30854,12 +30884,12 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V520" t="inlineStr">
+      <c r="Y520" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -30921,7 +30951,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -30936,7 +30966,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -30951,28 +30981,23 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:40:05</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J522" t="n">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="K522" t="n">
         <v>521</v>
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>VEGA PEREZ Melquisidec</t>
-        </is>
-      </c>
-      <c r="U522" t="inlineStr">
-        <is>
-          <t>80757</t>
+          <t>BARROSO Anna</t>
         </is>
       </c>
     </row>
@@ -31009,7 +31034,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>08:40:05</t>
+          <t>08:42:02</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -31018,21 +31043,21 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="K523" t="n">
         <v>522</v>
       </c>
       <c r="R523" t="inlineStr">
         <is>
-          <t>BARROSO Anna</t>
+          <t>GONZALEZ Clara</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -31062,7 +31087,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>08:42:02</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -31071,14 +31096,14 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K524" t="n">
         <v>523</v>
       </c>
       <c r="R524" t="inlineStr">
         <is>
-          <t>GONZALEZ Clara</t>
+          <t>ECHANIZ Pau</t>
         </is>
       </c>
     </row>
@@ -31115,7 +31140,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:46:02</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -31124,21 +31149,21 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K525" t="n">
         <v>524</v>
       </c>
       <c r="R525" t="inlineStr">
         <is>
-          <t>ECHANIZ Pau</t>
+          <t>OLAZABAL Telmo</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -31153,7 +31178,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -31168,23 +31193,28 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>08:46:02</t>
+          <t>09:03:01</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J526" t="n">
-        <v>292</v>
+        <v>210</v>
       </c>
       <c r="K526" t="n">
         <v>525</v>
       </c>
       <c r="R526" t="inlineStr">
         <is>
-          <t>OLAZABAL Telmo</t>
+          <t>JACQUET Claire</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>35684</t>
         </is>
       </c>
     </row>
@@ -31221,28 +31251,28 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>09:03:01</t>
+          <t>09:04:58</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J527" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="K527" t="n">
         <v>526</v>
       </c>
       <c r="R527" t="inlineStr">
         <is>
-          <t>JACQUET Claire</t>
-        </is>
-      </c>
-      <c r="U527" t="inlineStr">
-        <is>
-          <t>35684</t>
+          <t>SABATTINI Chiara</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>35219</t>
         </is>
       </c>
     </row>
@@ -31279,28 +31309,28 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>09:04:58</t>
+          <t>09:07:01</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J528" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K528" t="n">
         <v>527</v>
       </c>
       <c r="R528" t="inlineStr">
         <is>
-          <t>SABATTINI Chiara</t>
-        </is>
-      </c>
-      <c r="U528" t="inlineStr">
-        <is>
-          <t>35219</t>
+          <t>MINAZOVA Alsu</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>53314</t>
         </is>
       </c>
     </row>
@@ -31337,28 +31367,28 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>09:07:01</t>
+          <t>09:08:59</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J529" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="K529" t="n">
         <v>528</v>
       </c>
       <c r="R529" t="inlineStr">
         <is>
-          <t>MINAZOVA Alsu</t>
-        </is>
-      </c>
-      <c r="U529" t="inlineStr">
-        <is>
-          <t>53314</t>
+          <t>STOECKLIN Lena</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>35822</t>
         </is>
       </c>
     </row>
@@ -31395,28 +31425,28 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>09:08:59</t>
+          <t>09:11:01</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J530" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K530" t="n">
         <v>529</v>
       </c>
       <c r="R530" t="inlineStr">
         <is>
-          <t>STOECKLIN Lena</t>
-        </is>
-      </c>
-      <c r="U530" t="inlineStr">
-        <is>
-          <t>35822</t>
+          <t>LAZKANO Miren</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>35748</t>
         </is>
       </c>
     </row>
@@ -31453,28 +31483,28 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>09:11:01</t>
+          <t>09:13:01</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="J531" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="K531" t="n">
         <v>530</v>
       </c>
       <c r="R531" t="inlineStr">
         <is>
-          <t>LAZKANO Miren</t>
-        </is>
-      </c>
-      <c r="U531" t="inlineStr">
-        <is>
-          <t>35748</t>
+          <t>US Viktoriia</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>35528</t>
         </is>
       </c>
     </row>
@@ -31511,28 +31541,28 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>09:13:01</t>
+          <t>09:15:00</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="J532" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="K532" t="n">
         <v>531</v>
       </c>
       <c r="R532" t="inlineStr">
         <is>
-          <t>US Viktoriia</t>
-        </is>
-      </c>
-      <c r="U532" t="inlineStr">
-        <is>
-          <t>35528</t>
+          <t>JONES Luuka</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>36657</t>
         </is>
       </c>
     </row>
@@ -31569,28 +31599,28 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>09:15:00</t>
+          <t>09:16:59</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J533" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K533" t="n">
         <v>532</v>
       </c>
       <c r="R533" t="inlineStr">
         <is>
-          <t>JONES Luuka</t>
-        </is>
-      </c>
-      <c r="U533" t="inlineStr">
-        <is>
-          <t>36657</t>
+          <t>FOX Noemie</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>44812</t>
         </is>
       </c>
     </row>
@@ -31627,28 +31657,28 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>09:16:59</t>
+          <t>09:19:01</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J534" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K534" t="n">
         <v>533</v>
       </c>
       <c r="R534" t="inlineStr">
         <is>
-          <t>FOX Noemie</t>
-        </is>
-      </c>
-      <c r="U534" t="inlineStr">
-        <is>
-          <t>44812</t>
+          <t>PRIOUX Lucie</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>42984</t>
         </is>
       </c>
     </row>
@@ -31685,28 +31715,28 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>09:19:01</t>
+          <t>09:21:01</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J535" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K535" t="n">
         <v>534</v>
       </c>
       <c r="R535" t="inlineStr">
         <is>
-          <t>PRIOUX Lucie</t>
-        </is>
-      </c>
-      <c r="U535" t="inlineStr">
-        <is>
-          <t>42984</t>
+          <t>WERATSCHNIG Nadine</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>41613</t>
         </is>
       </c>
     </row>
@@ -31743,28 +31773,28 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>09:21:01</t>
+          <t>09:23:00</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J536" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="K536" t="n">
         <v>535</v>
       </c>
       <c r="R536" t="inlineStr">
         <is>
-          <t>WERATSCHNIG Nadine</t>
-        </is>
-      </c>
-      <c r="U536" t="inlineStr">
-        <is>
-          <t>41613</t>
+          <t>SKACHOVA Monika</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>53078</t>
         </is>
       </c>
     </row>
@@ -31801,7 +31831,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>09:23:00</t>
+          <t>09:25:00</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -31810,19 +31840,19 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K537" t="n">
         <v>536</v>
       </c>
       <c r="R537" t="inlineStr">
         <is>
-          <t>SKACHOVA Monika</t>
-        </is>
-      </c>
-      <c r="U537" t="inlineStr">
-        <is>
-          <t>53078</t>
+          <t>STANOVSKA Sona</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>51647</t>
         </is>
       </c>
     </row>
@@ -31859,28 +31889,28 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>09:25:00</t>
+          <t>09:27:01</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J538" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K538" t="n">
         <v>537</v>
       </c>
       <c r="R538" t="inlineStr">
         <is>
-          <t>STANOVSKA Sona</t>
-        </is>
-      </c>
-      <c r="U538" t="inlineStr">
-        <is>
-          <t>51647</t>
+          <t>SABITOVA Zulfia</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>40572</t>
         </is>
       </c>
     </row>
@@ -31917,28 +31947,28 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>09:27:01</t>
+          <t>09:29:00</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J539" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="K539" t="n">
         <v>538</v>
       </c>
       <c r="R539" t="inlineStr">
         <is>
-          <t>SABITOVA Zulfia</t>
-        </is>
-      </c>
-      <c r="U539" t="inlineStr">
-        <is>
-          <t>40572</t>
+          <t>BORGHI Elena</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>75493</t>
         </is>
       </c>
     </row>
@@ -31975,28 +32005,28 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>09:29:00</t>
+          <t>09:31:03</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J540" t="n">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="K540" t="n">
         <v>539</v>
       </c>
       <c r="R540" t="inlineStr">
         <is>
-          <t>BORGHI Elena</t>
-        </is>
-      </c>
-      <c r="U540" t="inlineStr">
-        <is>
-          <t>75493</t>
+          <t>HAVLICKOVA Katerina</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>35048</t>
         </is>
       </c>
     </row>
@@ -32033,28 +32063,28 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>09:31:03</t>
+          <t>09:32:58</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J541" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="K541" t="n">
         <v>540</v>
       </c>
       <c r="R541" t="inlineStr">
         <is>
-          <t>HAVLICKOVA Katerina</t>
-        </is>
-      </c>
-      <c r="U541" t="inlineStr">
-        <is>
-          <t>35048</t>
+          <t>GLEJTEKOVA Simona</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>55166</t>
         </is>
       </c>
     </row>
@@ -32091,28 +32121,28 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>09:32:58</t>
+          <t>09:35:00</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J542" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="K542" t="n">
         <v>541</v>
       </c>
       <c r="R542" t="inlineStr">
         <is>
-          <t>GLEJTEKOVA Simona</t>
-        </is>
-      </c>
-      <c r="U542" t="inlineStr">
-        <is>
-          <t>55166</t>
+          <t>BAUDU Lucie</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>35669</t>
         </is>
       </c>
     </row>
@@ -32149,28 +32179,28 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>09:36:58</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J543" t="n">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K543" t="n">
         <v>542</v>
       </c>
       <c r="R543" t="inlineStr">
         <is>
-          <t>BAUDU Lucie</t>
-        </is>
-      </c>
-      <c r="U543" t="inlineStr">
-        <is>
-          <t>35669</t>
+          <t>LAWRENCE Rosalyn</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>36531</t>
         </is>
       </c>
     </row>
@@ -32207,28 +32237,28 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>09:36:58</t>
+          <t>09:38:59</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J544" t="n">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="K544" t="n">
         <v>543</v>
       </c>
       <c r="R544" t="inlineStr">
         <is>
-          <t>LAWRENCE Rosalyn</t>
-        </is>
-      </c>
-      <c r="U544" t="inlineStr">
-        <is>
-          <t>36531</t>
+          <t>FORROW Bethan</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>69065</t>
         </is>
       </c>
     </row>
@@ -32265,28 +32295,28 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>09:38:59</t>
+          <t>09:41:00</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J545" t="n">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="K545" t="n">
         <v>544</v>
       </c>
       <c r="R545" t="inlineStr">
         <is>
-          <t>FORROW Bethan</t>
-        </is>
-      </c>
-      <c r="U545" t="inlineStr">
-        <is>
-          <t>69065</t>
+          <t>FOX Jessica</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>36526</t>
         </is>
       </c>
     </row>
@@ -32323,28 +32353,28 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>09:41:00</t>
+          <t>09:43:01</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J546" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="K546" t="n">
         <v>545</v>
       </c>
       <c r="R546" t="inlineStr">
         <is>
-          <t>FOX Jessica</t>
-        </is>
-      </c>
-      <c r="U546" t="inlineStr">
-        <is>
-          <t>36526</t>
+          <t>OLAZABAL Klara</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>43985</t>
         </is>
       </c>
     </row>
@@ -32381,28 +32411,28 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>09:43:01</t>
+          <t>09:45:00</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J547" t="n">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="K547" t="n">
         <v>546</v>
       </c>
       <c r="R547" t="inlineStr">
         <is>
-          <t>OLAZABAL Klara</t>
-        </is>
-      </c>
-      <c r="U547" t="inlineStr">
-        <is>
-          <t>43985</t>
+          <t>DELASSUS Marjorie</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>71964</t>
         </is>
       </c>
     </row>
@@ -32439,28 +32469,28 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>09:46:58</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J548" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="K548" t="n">
         <v>547</v>
       </c>
       <c r="R548" t="inlineStr">
         <is>
-          <t>DELASSUS Marjorie</t>
-        </is>
-      </c>
-      <c r="U548" t="inlineStr">
-        <is>
-          <t>71964</t>
+          <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
@@ -32497,28 +32527,28 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>09:46:58</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="J549" t="n">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="K549" t="n">
         <v>548</v>
       </c>
       <c r="R549" t="inlineStr">
         <is>
-          <t>FISEROVA Tereza</t>
-        </is>
-      </c>
-      <c r="U549" t="inlineStr">
-        <is>
-          <t>42016</t>
+          <t>DORIA VILARRUBLA Monica</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>53051</t>
         </is>
       </c>
     </row>
@@ -32555,28 +32585,28 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>09:49:00</t>
+          <t>09:50:58</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J550" t="n">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="K550" t="n">
         <v>549</v>
       </c>
       <c r="R550" t="inlineStr">
         <is>
-          <t>DORIA VILARRUBLA Monica</t>
-        </is>
-      </c>
-      <c r="U550" t="inlineStr">
-        <is>
-          <t>53051</t>
+          <t>WOLFFHARDT Viktoria</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>35303</t>
         </is>
       </c>
     </row>
@@ -32613,28 +32643,28 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>09:50:58</t>
+          <t>09:53:01</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J551" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K551" t="n">
         <v>550</v>
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>WOLFFHARDT Viktoria</t>
-        </is>
-      </c>
-      <c r="U551" t="inlineStr">
-        <is>
-          <t>35303</t>
+          <t>VILARRUBLA Nuria</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>35746</t>
         </is>
       </c>
     </row>
@@ -32671,28 +32701,28 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>09:53:01</t>
+          <t>09:54:58</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J552" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="K552" t="n">
         <v>551</v>
       </c>
       <c r="R552" t="inlineStr">
         <is>
-          <t>VILARRUBLA Nuria</t>
-        </is>
-      </c>
-      <c r="U552" t="inlineStr">
-        <is>
-          <t>35746</t>
+          <t>HERZOG Andrea</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>55099</t>
         </is>
       </c>
     </row>
@@ -32729,28 +32759,28 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>09:54:58</t>
+          <t>09:56:59</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J553" t="n">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K553" t="n">
         <v>552</v>
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>HERZOG Andrea</t>
-        </is>
-      </c>
-      <c r="U553" t="inlineStr">
-        <is>
-          <t>55099</t>
+          <t>WOODS Kimberley</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>35650</t>
         </is>
       </c>
     </row>
@@ -32787,28 +32817,28 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>09:56:59</t>
+          <t>09:59:02</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J554" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K554" t="n">
         <v>553</v>
       </c>
       <c r="R554" t="inlineStr">
         <is>
-          <t>WOODS Kimberley</t>
-        </is>
-      </c>
-      <c r="U554" t="inlineStr">
-        <is>
-          <t>35650</t>
+          <t>SATILA Ana</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>35327</t>
         </is>
       </c>
     </row>
@@ -32845,35 +32875,35 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>09:59:02</t>
+          <t>10:01:00</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K555" t="n">
         <v>554</v>
       </c>
       <c r="R555" t="inlineStr">
         <is>
-          <t>SATILA Ana</t>
-        </is>
-      </c>
-      <c r="U555" t="inlineStr">
-        <is>
-          <t>35327</t>
+          <t>FRANKLIN Mallory</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>35615</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -32883,7 +32913,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -32903,28 +32933,28 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>10:01:00</t>
+          <t>10:08:00</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J556" t="n">
-        <v>202</v>
+        <v>326</v>
       </c>
       <c r="K556" t="n">
         <v>555</v>
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>FRANKLIN Mallory</t>
-        </is>
-      </c>
-      <c r="U556" t="inlineStr">
-        <is>
-          <t>35615</t>
+          <t>HILGERT Lubos</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>35032</t>
         </is>
       </c>
     </row>
@@ -32961,28 +32991,28 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>10:08:00</t>
+          <t>10:09:56</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J557" t="n">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="K557" t="n">
         <v>556</v>
       </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>HILGERT Lubos</t>
-        </is>
-      </c>
-      <c r="U557" t="inlineStr">
-        <is>
-          <t>35032</t>
+          <t>JAKSE Zan</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>44340</t>
         </is>
       </c>
     </row>
@@ -33019,28 +33049,28 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>10:09:56</t>
+          <t>10:11:57</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J558" t="n">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="K558" t="n">
         <v>557</v>
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>JAKSE Zan</t>
-        </is>
-      </c>
-      <c r="U558" t="inlineStr">
-        <is>
-          <t>44340</t>
+          <t>IVALDI Zeno</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>35480</t>
         </is>
       </c>
     </row>
@@ -33077,28 +33107,28 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>10:11:57</t>
+          <t>10:13:59</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J559" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K559" t="n">
         <v>558</v>
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>IVALDI Zeno</t>
-        </is>
-      </c>
-      <c r="U559" t="inlineStr">
-        <is>
-          <t>35480</t>
+          <t>CRESPO Joan</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>35749</t>
         </is>
       </c>
     </row>
@@ -33135,28 +33165,28 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>10:13:59</t>
+          <t>10:15:59</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J560" t="n">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="K560" t="n">
         <v>559</v>
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>CRESPO Joan</t>
-        </is>
-      </c>
-      <c r="U560" t="inlineStr">
-        <is>
-          <t>35749</t>
+          <t>BOWERS Christopher</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>52010</t>
         </is>
       </c>
     </row>
@@ -33193,28 +33223,28 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>10:15:59</t>
+          <t>10:17:59</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="K561" t="n">
         <v>560</v>
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>BOWERS Christopher</t>
-        </is>
-      </c>
-      <c r="U561" t="inlineStr">
-        <is>
-          <t>52010</t>
+          <t>POLACZYK Mateusz</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>35072</t>
         </is>
       </c>
     </row>
@@ -33251,28 +33281,28 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>10:17:59</t>
+          <t>10:20:05</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J562" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K562" t="n">
         <v>561</v>
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>POLACZYK Mateusz</t>
-        </is>
-      </c>
-      <c r="U562" t="inlineStr">
-        <is>
-          <t>35072</t>
+          <t>EIGEL Pavel</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>35458</t>
         </is>
       </c>
     </row>
@@ -33309,28 +33339,28 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>10:20:05</t>
+          <t>10:21:58</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J563" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K563" t="n">
         <v>562</v>
       </c>
       <c r="R563" t="inlineStr">
         <is>
-          <t>EIGEL Pavel</t>
-        </is>
-      </c>
-      <c r="U563" t="inlineStr">
-        <is>
-          <t>35458</t>
+          <t>SRABOTNIK Martin</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>39080</t>
         </is>
       </c>
     </row>
@@ -33367,28 +33397,28 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>10:21:58</t>
+          <t>10:24:00</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J564" t="n">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="K564" t="n">
         <v>563</v>
       </c>
       <c r="R564" t="inlineStr">
         <is>
-          <t>SRABOTNIK Martin</t>
-        </is>
-      </c>
-      <c r="U564" t="inlineStr">
-        <is>
-          <t>39080</t>
+          <t>BIAZIZZO Mathieu</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>35484</t>
         </is>
       </c>
     </row>
@@ -33425,28 +33455,28 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:25:58</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J565" t="n">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="K565" t="n">
         <v>564</v>
       </c>
       <c r="R565" t="inlineStr">
         <is>
-          <t>BIAZIZZO Mathieu</t>
-        </is>
-      </c>
-      <c r="U565" t="inlineStr">
-        <is>
-          <t>35484</t>
+          <t>CLARKE Joseph</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>35654</t>
         </is>
       </c>
     </row>
@@ -33483,28 +33513,28 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>10:25:58</t>
+          <t>10:27:59</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J566" t="n">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="K566" t="n">
         <v>565</v>
       </c>
       <c r="R566" t="inlineStr">
         <is>
-          <t>CLARKE Joseph</t>
-        </is>
-      </c>
-      <c r="U566" t="inlineStr">
-        <is>
-          <t>35654</t>
+          <t>TESTEN Niko</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>39980</t>
         </is>
       </c>
     </row>
@@ -33541,28 +33571,28 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>10:27:59</t>
+          <t>10:29:59</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="J567" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="K567" t="n">
         <v>566</v>
       </c>
       <c r="R567" t="inlineStr">
         <is>
-          <t>TESTEN Niko</t>
-        </is>
-      </c>
-      <c r="U567" t="inlineStr">
-        <is>
-          <t>39980</t>
+          <t>BUTCHER Finn</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>36663</t>
         </is>
       </c>
     </row>
@@ -33599,28 +33629,28 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>10:29:59</t>
+          <t>10:31:57</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J568" t="n">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="K568" t="n">
         <v>567</v>
       </c>
       <c r="R568" t="inlineStr">
         <is>
-          <t>BUTCHER Finn</t>
-        </is>
-      </c>
-      <c r="U568" t="inlineStr">
-        <is>
-          <t>36663</t>
+          <t>HALCIN Martin</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>35355</t>
         </is>
       </c>
     </row>
@@ -33657,28 +33687,28 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>10:31:57</t>
+          <t>10:34:01</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J569" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K569" t="n">
         <v>568</v>
       </c>
       <c r="R569" t="inlineStr">
         <is>
-          <t>HALCIN Martin</t>
-        </is>
-      </c>
-      <c r="U569" t="inlineStr">
-        <is>
-          <t>35355</t>
+          <t>DOUGOUD Martin</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>35426</t>
         </is>
       </c>
     </row>
@@ -33715,28 +33745,28 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>10:34:01</t>
+          <t>10:36:01</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J570" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K570" t="n">
         <v>569</v>
       </c>
       <c r="R570" t="inlineStr">
         <is>
-          <t>DOUGOUD Martin</t>
-        </is>
-      </c>
-      <c r="U570" t="inlineStr">
-        <is>
-          <t>35426</t>
+          <t>MALEK Andrej</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>39246</t>
         </is>
       </c>
     </row>
@@ -33773,28 +33803,28 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>10:36:01</t>
+          <t>10:38:00</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J571" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K571" t="n">
         <v>570</v>
       </c>
       <c r="R571" t="inlineStr">
         <is>
-          <t>MALEK Andrej</t>
-        </is>
-      </c>
-      <c r="U571" t="inlineStr">
-        <is>
-          <t>39246</t>
+          <t>WERRO Lukas</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>35347</t>
         </is>
       </c>
     </row>
@@ -33831,28 +33861,28 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>10:38:00</t>
+          <t>10:40:00</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J572" t="n">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="K572" t="n">
         <v>571</v>
       </c>
       <c r="R572" t="inlineStr">
         <is>
-          <t>WERRO Lukas</t>
-        </is>
-      </c>
-      <c r="U572" t="inlineStr">
-        <is>
-          <t>35347</t>
+          <t>SCHUBERT Sebastian</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>35114</t>
         </is>
       </c>
     </row>
@@ -33889,28 +33919,28 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>10:40:00</t>
+          <t>10:41:59</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="J573" t="n">
-        <v>305</v>
+        <v>347</v>
       </c>
       <c r="K573" t="n">
         <v>572</v>
       </c>
       <c r="R573" t="inlineStr">
         <is>
-          <t>SCHUBERT Sebastian</t>
-        </is>
-      </c>
-      <c r="U573" t="inlineStr">
-        <is>
-          <t>35114</t>
+          <t>YAZAWA Kazuki</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>36482</t>
         </is>
       </c>
     </row>
@@ -33947,28 +33977,28 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>10:41:59</t>
+          <t>10:43:59</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="J574" t="n">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="K574" t="n">
         <v>573</v>
       </c>
       <c r="R574" t="inlineStr">
         <is>
-          <t>YAZAWA Kazuki</t>
-        </is>
-      </c>
-      <c r="U574" t="inlineStr">
-        <is>
-          <t>36482</t>
+          <t>TSVIET Igor</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>35527</t>
         </is>
       </c>
     </row>
@@ -34005,28 +34035,28 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>10:43:59</t>
+          <t>10:46:01</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J575" t="n">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K575" t="n">
         <v>574</v>
       </c>
       <c r="R575" t="inlineStr">
         <is>
-          <t>TSVIET Igor</t>
-        </is>
-      </c>
-      <c r="U575" t="inlineStr">
-        <is>
-          <t>35527</t>
+          <t>BURGI Quentin</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>41590</t>
         </is>
       </c>
     </row>
@@ -34043,17 +34073,17 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -34063,28 +34093,28 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>10:45:00</t>
+          <t>10:47:59</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="J576" t="n">
-        <v>58</v>
+        <v>318</v>
       </c>
       <c r="K576" t="n">
         <v>575</v>
       </c>
       <c r="R576" t="inlineStr">
         <is>
-          <t>VEGA PEREZ Melquisidec</t>
-        </is>
-      </c>
-      <c r="U576" t="inlineStr">
-        <is>
-          <t>80757</t>
+          <t>ADACHI Kazuya</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>36646</t>
         </is>
       </c>
     </row>
@@ -34121,28 +34151,28 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>10:46:01</t>
+          <t>10:49:57</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J577" t="n">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="K577" t="n">
         <v>576</v>
       </c>
       <c r="R577" t="inlineStr">
         <is>
-          <t>BURGI Quentin</t>
-        </is>
-      </c>
-      <c r="U577" t="inlineStr">
-        <is>
-          <t>41590</t>
+          <t>OSCHMAUTZ Felix</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>51856</t>
         </is>
       </c>
     </row>
@@ -34179,28 +34209,28 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>10:47:59</t>
+          <t>10:51:58</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J578" t="n">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="K578" t="n">
         <v>577</v>
       </c>
       <c r="R578" t="inlineStr">
         <is>
-          <t>ADACHI Kazuya</t>
-        </is>
-      </c>
-      <c r="U578" t="inlineStr">
-        <is>
-          <t>36646</t>
+          <t>MADORE Mathurin</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>51994</t>
         </is>
       </c>
     </row>
@@ -34237,28 +34267,28 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>10:49:57</t>
+          <t>10:53:59</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J579" t="n">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="K579" t="n">
         <v>578</v>
       </c>
       <c r="R579" t="inlineStr">
         <is>
-          <t>OSCHMAUTZ Felix</t>
-        </is>
-      </c>
-      <c r="U579" t="inlineStr">
-        <is>
-          <t>51856</t>
+          <t>AIGNER Hannes</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>35115</t>
         </is>
       </c>
     </row>
@@ -34295,28 +34325,28 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>10:51:58</t>
+          <t>10:56:00</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="K580" t="n">
         <v>579</v>
       </c>
       <c r="R580" t="inlineStr">
         <is>
-          <t>MADORE Mathurin</t>
-        </is>
-      </c>
-      <c r="U580" t="inlineStr">
-        <is>
-          <t>51994</t>
+          <t>HAYWARD Ben</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>35539</t>
         </is>
       </c>
     </row>
@@ -34353,28 +34383,28 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>10:53:59</t>
+          <t>10:57:58</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J581" t="n">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="K581" t="n">
         <v>580</v>
       </c>
       <c r="R581" t="inlineStr">
         <is>
-          <t>AIGNER Hannes</t>
-        </is>
-      </c>
-      <c r="U581" t="inlineStr">
-        <is>
-          <t>35115</t>
+          <t>LEITNER Mario</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>35546</t>
         </is>
       </c>
     </row>
@@ -34411,28 +34441,28 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:59:59</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J582" t="n">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="K582" t="n">
         <v>581</v>
       </c>
       <c r="R582" t="inlineStr">
         <is>
-          <t>HAYWARD Ben</t>
-        </is>
-      </c>
-      <c r="U582" t="inlineStr">
-        <is>
-          <t>35539</t>
+          <t>GRIGAR Jakub</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>37284</t>
         </is>
       </c>
     </row>
@@ -34469,28 +34499,28 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>10:57:58</t>
+          <t>11:02:01</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J583" t="n">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="K583" t="n">
         <v>582</v>
       </c>
       <c r="R583" t="inlineStr">
         <is>
-          <t>LEITNER Mario</t>
-        </is>
-      </c>
-      <c r="U583" t="inlineStr">
-        <is>
-          <t>35546</t>
+          <t>FORBES-CRYANS Bradley</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>36513</t>
         </is>
       </c>
     </row>
@@ -34527,28 +34557,28 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>10:59:59</t>
+          <t>11:03:57</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J584" t="n">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="K584" t="n">
         <v>583</v>
       </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>GRIGAR Jakub</t>
-        </is>
-      </c>
-      <c r="U584" t="inlineStr">
-        <is>
-          <t>37284</t>
+          <t>HOLMER Erik</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>35104</t>
         </is>
       </c>
     </row>
@@ -34585,28 +34615,28 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>11:02:01</t>
+          <t>11:05:57</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="J585" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K585" t="n">
         <v>584</v>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>FORBES-CRYANS Bradley</t>
-        </is>
-      </c>
-      <c r="U585" t="inlineStr">
-        <is>
-          <t>36513</t>
+          <t>BERSINGER Thomas</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>35228</t>
         </is>
       </c>
     </row>
@@ -34643,28 +34673,28 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>11:03:57</t>
+          <t>11:07:59</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J586" t="n">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="K586" t="n">
         <v>585</v>
       </c>
       <c r="R586" t="inlineStr">
         <is>
-          <t>HOLMER Erik</t>
-        </is>
-      </c>
-      <c r="U586" t="inlineStr">
-        <is>
-          <t>35104</t>
+          <t>LLORENTE David</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>51850</t>
         </is>
       </c>
     </row>
@@ -34701,28 +34731,28 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>11:05:57</t>
+          <t>11:09:59</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J587" t="n">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="K587" t="n">
         <v>586</v>
       </c>
       <c r="R587" t="inlineStr">
         <is>
-          <t>BERSINGER Thomas</t>
-        </is>
-      </c>
-      <c r="U587" t="inlineStr">
-        <is>
-          <t>35228</t>
+          <t>HERNANZ Samuel</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>35786</t>
         </is>
       </c>
     </row>
@@ -34759,28 +34789,28 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>11:07:59</t>
+          <t>11:12:00</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J588" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="K588" t="n">
         <v>587</v>
       </c>
       <c r="R588" t="inlineStr">
         <is>
-          <t>LLORENTE David</t>
-        </is>
-      </c>
-      <c r="U588" t="inlineStr">
-        <is>
-          <t>51850</t>
+          <t>POPIELA Dariusz</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>35096</t>
         </is>
       </c>
     </row>
@@ -34817,28 +34847,28 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>11:09:59</t>
+          <t>11:13:58</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J589" t="n">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="K589" t="n">
         <v>588</v>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>HERNANZ Samuel</t>
-        </is>
-      </c>
-      <c r="U589" t="inlineStr">
-        <is>
-          <t>35786</t>
+          <t>DE GENNARO Giovanni</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>35244</t>
         </is>
       </c>
     </row>
@@ -34875,28 +34905,28 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>11:12:00</t>
+          <t>11:16:00</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J590" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="K590" t="n">
         <v>589</v>
       </c>
       <c r="R590" t="inlineStr">
         <is>
-          <t>POPIELA Dariusz</t>
-        </is>
-      </c>
-      <c r="U590" t="inlineStr">
-        <is>
-          <t>35096</t>
+          <t>PRINDIS Vit</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>35065</t>
         </is>
       </c>
     </row>
@@ -34933,28 +34963,28 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>11:13:58</t>
+          <t>11:17:59</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="J591" t="n">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="K591" t="n">
         <v>590</v>
       </c>
       <c r="R591" t="inlineStr">
         <is>
-          <t>DE GENNARO Giovanni</t>
-        </is>
-      </c>
-      <c r="U591" t="inlineStr">
-        <is>
-          <t>35244</t>
+          <t>LAUNAY Antoine</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>68776</t>
         </is>
       </c>
     </row>
@@ -34991,28 +35021,28 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>11:16:00</t>
+          <t>11:19:57</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J592" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K592" t="n">
         <v>591</v>
       </c>
       <c r="R592" t="inlineStr">
         <is>
-          <t>PRINDIS Vit</t>
-        </is>
-      </c>
-      <c r="U592" t="inlineStr">
-        <is>
-          <t>35065</t>
+          <t>KAUZER Peter</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>35589</t>
         </is>
       </c>
     </row>
@@ -35049,28 +35079,28 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>11:17:59</t>
+          <t>11:21:57</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J593" t="n">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="K593" t="n">
         <v>592</v>
       </c>
       <c r="R593" t="inlineStr">
         <is>
-          <t>LAUNAY Antoine</t>
-        </is>
-      </c>
-      <c r="U593" t="inlineStr">
-        <is>
-          <t>68776</t>
+          <t>DELFOUR Lucien</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>36537</t>
         </is>
       </c>
     </row>
@@ -35107,28 +35137,28 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>11:19:57</t>
+          <t>11:23:58</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J594" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K594" t="n">
         <v>593</v>
       </c>
       <c r="R594" t="inlineStr">
         <is>
-          <t>KAUZER Peter</t>
-        </is>
-      </c>
-      <c r="U594" t="inlineStr">
-        <is>
-          <t>35589</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -35165,35 +35195,35 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>11:21:57</t>
+          <t>11:25:59</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J595" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K595" t="n">
         <v>594</v>
       </c>
       <c r="R595" t="inlineStr">
         <is>
-          <t>DELFOUR Lucien</t>
-        </is>
-      </c>
-      <c r="U595" t="inlineStr">
-        <is>
-          <t>36537</t>
+          <t>NEVEU Boris</t>
+        </is>
+      </c>
+      <c r="X595" t="inlineStr">
+        <is>
+          <t>35396</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -35203,12 +35233,12 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -35223,35 +35253,45 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>11:23:58</t>
+          <t>12:02:59</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J596" t="n">
-        <v>303</v>
+        <v>213</v>
       </c>
       <c r="K596" t="n">
         <v>595</v>
       </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R596" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U596" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>FOX Noemie</t>
+        </is>
+      </c>
+      <c r="X596" t="inlineStr">
+        <is>
+          <t>44812</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -35261,12 +35301,12 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -35281,28 +35321,38 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>11:25:59</t>
+          <t>12:05:59</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J597" t="n">
-        <v>311</v>
+        <v>217</v>
       </c>
       <c r="K597" t="n">
         <v>596</v>
       </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>NEVEU Boris</t>
-        </is>
-      </c>
-      <c r="U597" t="inlineStr">
-        <is>
-          <t>35396</t>
+          <t>HERZOG Andrea</t>
+        </is>
+      </c>
+      <c r="X597" t="inlineStr">
+        <is>
+          <t>55099</t>
         </is>
       </c>
     </row>
@@ -35339,38 +35389,38 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>12:02:59</t>
+          <t>12:09:01</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J598" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="K598" t="n">
         <v>597</v>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>FOX Noemie</t>
-        </is>
-      </c>
-      <c r="U598" t="inlineStr">
-        <is>
-          <t>44812</t>
+          <t>MINAZOVA Alsu</t>
+        </is>
+      </c>
+      <c r="X598" t="inlineStr">
+        <is>
+          <t>53314</t>
         </is>
       </c>
     </row>
@@ -35407,38 +35457,38 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>12:05:59</t>
+          <t>12:11:57</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J599" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="K599" t="n">
         <v>598</v>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>HERZOG Andrea</t>
-        </is>
-      </c>
-      <c r="U599" t="inlineStr">
-        <is>
-          <t>55099</t>
+          <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X599" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
@@ -35475,38 +35525,38 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>12:09:01</t>
+          <t>12:14:59</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J600" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="K600" t="n">
         <v>599</v>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>MINAZOVA Alsu</t>
-        </is>
-      </c>
-      <c r="U600" t="inlineStr">
-        <is>
-          <t>53314</t>
+          <t>WOLFFHARDT Viktoria</t>
+        </is>
+      </c>
+      <c r="X600" t="inlineStr">
+        <is>
+          <t>35303</t>
         </is>
       </c>
     </row>
@@ -35543,38 +35593,38 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>12:11:57</t>
+          <t>12:19:59</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="J601" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K601" t="n">
         <v>600</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>FISEROVA Tereza</t>
-        </is>
-      </c>
-      <c r="U601" t="inlineStr">
-        <is>
-          <t>42016</t>
+          <t>JONES Luuka</t>
+        </is>
+      </c>
+      <c r="X601" t="inlineStr">
+        <is>
+          <t>36657</t>
         </is>
       </c>
     </row>
@@ -35611,38 +35661,38 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>12:14:59</t>
+          <t>12:23:00</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="J602" t="n">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="K602" t="n">
         <v>601</v>
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>WOLFFHARDT Viktoria</t>
-        </is>
-      </c>
-      <c r="U602" t="inlineStr">
-        <is>
-          <t>35303</t>
+          <t>DORIA VILARRUBLA Monica</t>
+        </is>
+      </c>
+      <c r="X602" t="inlineStr">
+        <is>
+          <t>53051</t>
         </is>
       </c>
     </row>
@@ -35679,38 +35729,38 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>12:19:59</t>
+          <t>12:26:02</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J603" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K603" t="n">
         <v>602</v>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>JONES Luuka</t>
-        </is>
-      </c>
-      <c r="U603" t="inlineStr">
-        <is>
-          <t>36657</t>
+          <t>WERATSCHNIG Nadine</t>
+        </is>
+      </c>
+      <c r="X603" t="inlineStr">
+        <is>
+          <t>41613</t>
         </is>
       </c>
     </row>
@@ -35747,38 +35797,38 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>12:23:00</t>
+          <t>12:29:00</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J604" t="n">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="K604" t="n">
         <v>603</v>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>DORIA VILARRUBLA Monica</t>
-        </is>
-      </c>
-      <c r="U604" t="inlineStr">
-        <is>
-          <t>53051</t>
+          <t>FRANKLIN Mallory</t>
+        </is>
+      </c>
+      <c r="X604" t="inlineStr">
+        <is>
+          <t>35615</t>
         </is>
       </c>
     </row>
@@ -35815,45 +35865,45 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>12:26:02</t>
+          <t>12:32:00</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J605" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="K605" t="n">
         <v>604</v>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>WERATSCHNIG Nadine</t>
-        </is>
-      </c>
-      <c r="U605" t="inlineStr">
-        <is>
-          <t>41613</t>
+          <t>FOX Jessica</t>
+        </is>
+      </c>
+      <c r="X605" t="inlineStr">
+        <is>
+          <t>36526</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -35863,7 +35913,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -35883,16 +35933,16 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>12:29:00</t>
+          <t>12:39:57</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J606" t="n">
-        <v>202</v>
+        <v>309</v>
       </c>
       <c r="K606" t="n">
         <v>605</v>
@@ -35909,19 +35959,19 @@
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>FRANKLIN Mallory</t>
-        </is>
-      </c>
-      <c r="U606" t="inlineStr">
-        <is>
-          <t>35615</t>
+          <t>DELFOUR Lucien</t>
+        </is>
+      </c>
+      <c r="X606" t="inlineStr">
+        <is>
+          <t>36537</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -35931,7 +35981,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -35951,16 +36001,16 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>12:32:00</t>
+          <t>12:42:56</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J607" t="n">
-        <v>201</v>
+        <v>312</v>
       </c>
       <c r="K607" t="n">
         <v>606</v>
@@ -35977,12 +36027,12 @@
       </c>
       <c r="R607" t="inlineStr">
         <is>
-          <t>FOX Jessica</t>
-        </is>
-      </c>
-      <c r="U607" t="inlineStr">
-        <is>
-          <t>36526</t>
+          <t>DE GENNARO Giovanni</t>
+        </is>
+      </c>
+      <c r="X607" t="inlineStr">
+        <is>
+          <t>35244</t>
         </is>
       </c>
     </row>
@@ -36019,38 +36069,38 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>12:39:57</t>
+          <t>12:46:00</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J608" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K608" t="n">
         <v>607</v>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R608" t="inlineStr">
         <is>
-          <t>DELFOUR Lucien</t>
-        </is>
-      </c>
-      <c r="U608" t="inlineStr">
-        <is>
-          <t>36537</t>
+          <t>AIGNER Hannes</t>
+        </is>
+      </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>35115</t>
         </is>
       </c>
     </row>
@@ -36087,38 +36137,38 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>12:42:56</t>
+          <t>12:49:00</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J609" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="K609" t="n">
         <v>608</v>
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>DE GENNARO Giovanni</t>
-        </is>
-      </c>
-      <c r="U609" t="inlineStr">
-        <is>
-          <t>35244</t>
+          <t>DOUGOUD Martin</t>
+        </is>
+      </c>
+      <c r="X609" t="inlineStr">
+        <is>
+          <t>35426</t>
         </is>
       </c>
     </row>
@@ -36155,38 +36205,38 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>12:46:00</t>
+          <t>12:51:58</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J610" t="n">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="K610" t="n">
         <v>609</v>
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R610" t="inlineStr">
         <is>
-          <t>AIGNER Hannes</t>
-        </is>
-      </c>
-      <c r="U610" t="inlineStr">
-        <is>
-          <t>35115</t>
+          <t>TESTEN Niko</t>
+        </is>
+      </c>
+      <c r="X610" t="inlineStr">
+        <is>
+          <t>39980</t>
         </is>
       </c>
     </row>
@@ -36223,38 +36273,38 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>12:49:00</t>
+          <t>12:56:59</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J611" t="n">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="K611" t="n">
         <v>610</v>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R611" t="inlineStr">
         <is>
-          <t>DOUGOUD Martin</t>
-        </is>
-      </c>
-      <c r="U611" t="inlineStr">
-        <is>
-          <t>35426</t>
+          <t>PRINDIS Vit</t>
+        </is>
+      </c>
+      <c r="X611" t="inlineStr">
+        <is>
+          <t>35065</t>
         </is>
       </c>
     </row>
@@ -36291,38 +36341,38 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>12:51:58</t>
+          <t>12:59:59</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J612" t="n">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="K612" t="n">
         <v>611</v>
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R612" t="inlineStr">
         <is>
-          <t>TESTEN Niko</t>
-        </is>
-      </c>
-      <c r="U612" t="inlineStr">
-        <is>
-          <t>39980</t>
+          <t>CRESPO Joan</t>
+        </is>
+      </c>
+      <c r="X612" t="inlineStr">
+        <is>
+          <t>35749</t>
         </is>
       </c>
     </row>
@@ -36359,7 +36409,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>12:56:59</t>
+          <t>13:02:56</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -36368,29 +36418,29 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K613" t="n">
         <v>612</v>
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R613" t="inlineStr">
         <is>
-          <t>PRINDIS Vit</t>
-        </is>
-      </c>
-      <c r="U613" t="inlineStr">
-        <is>
-          <t>35065</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X613" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -36427,7 +36477,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>12:59:59</t>
+          <t>13:05:59</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -36436,29 +36486,29 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K614" t="n">
         <v>613</v>
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R614" t="inlineStr">
         <is>
-          <t>CRESPO Joan</t>
-        </is>
-      </c>
-      <c r="U614" t="inlineStr">
-        <is>
-          <t>35749</t>
+          <t>LLORENTE David</t>
+        </is>
+      </c>
+      <c r="X614" t="inlineStr">
+        <is>
+          <t>51850</t>
         </is>
       </c>
     </row>
@@ -36495,45 +36545,45 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>13:02:56</t>
+          <t>13:08:58</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J615" t="n">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="K615" t="n">
         <v>614</v>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R615" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U615" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>BIAZIZZO Mathieu</t>
+        </is>
+      </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>35484</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -36543,12 +36593,12 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
@@ -36563,532 +36613,38 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>13:05:59</t>
+          <t>14:40:00</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J616" t="n">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="K616" t="n">
         <v>615</v>
       </c>
-      <c r="M616" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N616" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R616" t="inlineStr">
         <is>
-          <t>LLORENTE David</t>
-        </is>
-      </c>
-      <c r="U616" t="inlineStr">
-        <is>
-          <t>51850</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E617" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F617" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G617" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H617" t="inlineStr">
-        <is>
-          <t>13:08:58</t>
-        </is>
-      </c>
-      <c r="I617" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J617" t="n">
-        <v>314</v>
-      </c>
-      <c r="K617" t="n">
-        <v>616</v>
-      </c>
-      <c r="M617" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N617" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R617" t="inlineStr">
-        <is>
-          <t>BIAZIZZO Mathieu</t>
-        </is>
-      </c>
-      <c r="U617" t="inlineStr">
-        <is>
-          <t>35484</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E618" t="inlineStr">
-        <is>
-          <t>Semifinal</t>
-        </is>
-      </c>
-      <c r="F618" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G618" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H618" t="inlineStr">
-        <is>
-          <t>14:32:00</t>
-        </is>
-      </c>
-      <c r="I618" t="inlineStr">
-        <is>
-          <t>NED</t>
-        </is>
-      </c>
-      <c r="J618" t="n">
-        <v>407</v>
-      </c>
-      <c r="K618" t="n">
-        <v>617</v>
-      </c>
-      <c r="R618" t="inlineStr">
-        <is>
-          <t>OTTEN Maartje</t>
-        </is>
-      </c>
-      <c r="S618" t="inlineStr">
-        <is>
-          <t>OTTEN Joris</t>
-        </is>
-      </c>
-      <c r="U618" t="inlineStr">
-        <is>
-          <t>35337</t>
-        </is>
-      </c>
-      <c r="V618" t="inlineStr">
-        <is>
-          <t>41698</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>Semifinal</t>
-        </is>
-      </c>
-      <c r="F619" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G619" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H619" t="inlineStr">
-        <is>
-          <t>14:40:00</t>
-        </is>
-      </c>
-      <c r="I619" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J619" t="n">
-        <v>403</v>
-      </c>
-      <c r="K619" t="n">
-        <v>618</v>
-      </c>
-      <c r="R619" t="inlineStr">
-        <is>
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="S619" t="inlineStr">
+      <c r="S616" t="inlineStr">
         <is>
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V619" t="inlineStr">
+      <c r="Y616" t="inlineStr">
         <is>
           <t>51995</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F620" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G620" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H620" t="inlineStr">
-        <is>
-          <t>14:44:00</t>
-        </is>
-      </c>
-      <c r="I620" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="J620" t="n">
-        <v>376</v>
-      </c>
-      <c r="K620" t="n">
-        <v>619</v>
-      </c>
-      <c r="R620" t="inlineStr">
-        <is>
-          <t>VEGA PEREZ Melquisidec</t>
-        </is>
-      </c>
-      <c r="U620" t="inlineStr">
-        <is>
-          <t>80757</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G621" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>15:08:00</t>
-        </is>
-      </c>
-      <c r="I621" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-      <c r="J621" t="n">
-        <v>352</v>
-      </c>
-      <c r="K621" t="n">
-        <v>620</v>
-      </c>
-      <c r="R621" t="inlineStr">
-        <is>
-          <t>STANOVSKY Martin</t>
-        </is>
-      </c>
-      <c r="U621" t="inlineStr">
-        <is>
-          <t>68782</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E622" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G622" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H622" t="inlineStr">
-        <is>
-          <t>15:27:00</t>
-        </is>
-      </c>
-      <c r="I622" t="inlineStr">
-        <is>
-          <t>SLO</t>
-        </is>
-      </c>
-      <c r="J622" t="n">
-        <v>333</v>
-      </c>
-      <c r="K622" t="n">
-        <v>621</v>
-      </c>
-      <c r="R622" t="inlineStr">
-        <is>
-          <t>SRABOTNIK Martin</t>
-        </is>
-      </c>
-      <c r="U622" t="inlineStr">
-        <is>
-          <t>39080</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F623" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G623" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H623" t="inlineStr">
-        <is>
-          <t>16:49:00</t>
-        </is>
-      </c>
-      <c r="I623" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="J623" t="n">
-        <v>376</v>
-      </c>
-      <c r="K623" t="n">
-        <v>622</v>
-      </c>
-      <c r="R623" t="inlineStr">
-        <is>
-          <t>VEGA PEREZ Melquisidec</t>
-        </is>
-      </c>
-      <c r="U623" t="inlineStr">
-        <is>
-          <t>80757</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>Heats</t>
-        </is>
-      </c>
-      <c r="F624" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G624" t="inlineStr">
-        <is>
-          <t>2018-09-09</t>
-        </is>
-      </c>
-      <c r="H624" t="inlineStr">
-        <is>
-          <t>17:12:00</t>
-        </is>
-      </c>
-      <c r="I624" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-      <c r="J624" t="n">
-        <v>352</v>
-      </c>
-      <c r="K624" t="n">
-        <v>623</v>
-      </c>
-      <c r="R624" t="inlineStr">
-        <is>
-          <t>STANOVSKY Martin</t>
-        </is>
-      </c>
-      <c r="U624" t="inlineStr">
-        <is>
-          <t>68782</t>
         </is>
       </c>
     </row>

--- a/events/LaSeu_2018_WC/LaSeu_2018_WC_start.xlsx
+++ b/events/LaSeu_2018_WC/LaSeu_2018_WC_start.xlsx
@@ -30227,6 +30227,11 @@
           <t>35079</t>
         </is>
       </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>61261</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -30353,6 +30358,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y513" t="inlineStr">
         <is>
           <t>35061</t>
@@ -30582,6 +30592,11 @@
           <t>JANE Jakub</t>
         </is>
       </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
       <c r="Y516" t="inlineStr">
         <is>
           <t>35061</t>
@@ -30814,6 +30829,11 @@
       <c r="X519" t="inlineStr">
         <is>
           <t>35079</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>61261</t>
         </is>
       </c>
     </row>
